--- a/VerveStacks_VNM_grids_kan/vt_vervestacks_VNM_v1.xlsx
+++ b/VerveStacks_VNM_grids_kan/vt_vervestacks_VNM_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{278EC894-F97F-497C-8616-6D58E7FE0FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C72A6E0C-8663-4D1B-B50A-75D5A5DF113A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{79A68F94-2D9A-4393-88AC-A1DC12C46C9E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{930809CF-90FC-411C-81D2-FB561E31C520}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -92,13 +92,13 @@
     <t>e_VN1054-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_VN1054-500__ember</t>
+    <t>ep_bioenergy_VN1054-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_VN98-220</t>
   </si>
   <si>
-    <t>ep_bioenergy_VN98-220__ember</t>
+    <t>ep_bioenergy_VN98-220__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w1046230185-220</t>
@@ -107,7 +107,7 @@
     <t>e_w1046230185-220</t>
   </si>
   <si>
-    <t>ep_bioenergy_w1046230185-220__ember</t>
+    <t>ep_bioenergy_w1046230185-220__irena</t>
   </si>
   <si>
     <t>ep_coal_CFB_G100000100190</t>
@@ -1472,13 +1472,13 @@
     <t>yes</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - VN1054-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - VN98-220_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1046230185-220_Missing Bioenergy Capacity -- operating</t>
+    <t>Aggregated Plant - IRENA Gap - VN1054-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - VN98-220_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1046230185-220_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
     <t>An Khanh power station_Phase 1 Unit 1 -- operating</t>
@@ -4186,7 +4186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E523C2A-4DF2-4C82-8E4B-13001CB2C3A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DD836A-BF91-4DF7-BEC5-3FD283E16575}">
   <dimension ref="B9:T117"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E11">
-        <v>0.13547735999999996</v>
+        <v>0.13681871999999998</v>
       </c>
       <c r="F11">
         <v>3144</v>
@@ -4321,7 +4321,7 @@
         <v>25</v>
       </c>
       <c r="E12">
-        <v>0.13547735999999996</v>
+        <v>0.13681871999999998</v>
       </c>
       <c r="F12">
         <v>3144</v>
@@ -4377,7 +4377,7 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>0.17961839999999998</v>
+        <v>0.1813968</v>
       </c>
       <c r="F13">
         <v>2757</v>
@@ -4433,7 +4433,7 @@
         <v>28</v>
       </c>
       <c r="E14">
-        <v>0.17961839999999998</v>
+        <v>0.1813968</v>
       </c>
       <c r="F14">
         <v>2757</v>
@@ -4489,7 +4489,7 @@
         <v>31</v>
       </c>
       <c r="E15">
-        <v>0.17003875199999999</v>
+        <v>0.17172230399999996</v>
       </c>
       <c r="F15">
         <v>2757</v>
@@ -4545,7 +4545,7 @@
         <v>31</v>
       </c>
       <c r="E16">
-        <v>0.17003875199999999</v>
+        <v>0.17172230399999996</v>
       </c>
       <c r="F16">
         <v>2757</v>
@@ -4601,7 +4601,7 @@
         <v>34</v>
       </c>
       <c r="E17">
-        <v>0.17482857599999999</v>
+        <v>0.17655955200000001</v>
       </c>
       <c r="F17">
         <v>2757</v>
@@ -4657,7 +4657,7 @@
         <v>34</v>
       </c>
       <c r="E18">
-        <v>0.13547735999999999</v>
+        <v>0.13681871999999998</v>
       </c>
       <c r="F18">
         <v>3144</v>
@@ -4713,7 +4713,7 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>0.13547735999999999</v>
+        <v>0.13681871999999998</v>
       </c>
       <c r="F19">
         <v>3144</v>
@@ -4769,7 +4769,7 @@
         <v>38</v>
       </c>
       <c r="E20">
-        <v>0.17003875199999999</v>
+        <v>0.17172230399999999</v>
       </c>
       <c r="F20">
         <v>2757</v>
@@ -4825,7 +4825,7 @@
         <v>38</v>
       </c>
       <c r="E21">
-        <v>0.17003875199999999</v>
+        <v>0.17172230399999999</v>
       </c>
       <c r="F21">
         <v>2757</v>
@@ -4881,7 +4881,7 @@
         <v>41</v>
       </c>
       <c r="E22">
-        <v>0.10170085920000003</v>
+        <v>0.10270779840000001</v>
       </c>
       <c r="F22">
         <v>3583</v>
@@ -4937,7 +4937,7 @@
         <v>25</v>
       </c>
       <c r="E23">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F23">
         <v>3144</v>
@@ -4993,7 +4993,7 @@
         <v>25</v>
       </c>
       <c r="E24">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F24">
         <v>3144</v>
@@ -5049,7 +5049,7 @@
         <v>45</v>
       </c>
       <c r="E25">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F25">
         <v>1967</v>
@@ -5105,7 +5105,7 @@
         <v>45</v>
       </c>
       <c r="E26">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F26">
         <v>1967</v>
@@ -5161,7 +5161,7 @@
         <v>45</v>
       </c>
       <c r="E27">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F27">
         <v>1967</v>
@@ -5217,7 +5217,7 @@
         <v>49</v>
       </c>
       <c r="E28">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F28">
         <v>3144</v>
@@ -5273,7 +5273,7 @@
         <v>49</v>
       </c>
       <c r="E29">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F29">
         <v>3144</v>
@@ -5329,7 +5329,7 @@
         <v>49</v>
       </c>
       <c r="E30">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F30">
         <v>3144</v>
@@ -5385,7 +5385,7 @@
         <v>53</v>
       </c>
       <c r="E31">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F31">
         <v>1967</v>
@@ -5441,7 +5441,7 @@
         <v>53</v>
       </c>
       <c r="E32">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F32">
         <v>1967</v>
@@ -5497,7 +5497,7 @@
         <v>56</v>
       </c>
       <c r="E33">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F33">
         <v>3144</v>
@@ -5553,7 +5553,7 @@
         <v>56</v>
       </c>
       <c r="E34">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F34">
         <v>3144</v>
@@ -5609,7 +5609,7 @@
         <v>56</v>
       </c>
       <c r="E35">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F35">
         <v>3144</v>
@@ -5665,7 +5665,7 @@
         <v>56</v>
       </c>
       <c r="E36">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F36">
         <v>3144</v>
@@ -5721,7 +5721,7 @@
         <v>61</v>
       </c>
       <c r="E37">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F37">
         <v>1967</v>
@@ -5777,7 +5777,7 @@
         <v>61</v>
       </c>
       <c r="E38">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F38">
         <v>1967</v>
@@ -5833,7 +5833,7 @@
         <v>61</v>
       </c>
       <c r="E39">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F39">
         <v>1967</v>
@@ -5889,7 +5889,7 @@
         <v>61</v>
       </c>
       <c r="E40">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F40">
         <v>1967</v>
@@ -5945,7 +5945,7 @@
         <v>34</v>
       </c>
       <c r="E41">
-        <v>0.12958704000000001</v>
+        <v>0.13087008</v>
       </c>
       <c r="F41">
         <v>3144</v>
@@ -6001,7 +6001,7 @@
         <v>34</v>
       </c>
       <c r="E42">
-        <v>0.12958704000000001</v>
+        <v>0.13087008</v>
       </c>
       <c r="F42">
         <v>3144</v>
@@ -6057,7 +6057,7 @@
         <v>68</v>
       </c>
       <c r="E43">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F43">
         <v>3144</v>
@@ -6113,7 +6113,7 @@
         <v>68</v>
       </c>
       <c r="E44">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F44">
         <v>3144</v>
@@ -6169,7 +6169,7 @@
         <v>71</v>
       </c>
       <c r="E45">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F45">
         <v>3144</v>
@@ -6225,7 +6225,7 @@
         <v>73</v>
       </c>
       <c r="E46">
-        <v>0.12958704000000001</v>
+        <v>0.13087008</v>
       </c>
       <c r="F46">
         <v>3144</v>
@@ -6281,7 +6281,7 @@
         <v>75</v>
       </c>
       <c r="E47">
-        <v>0.12958704000000001</v>
+        <v>0.13087008</v>
       </c>
       <c r="F47">
         <v>3144</v>
@@ -6337,7 +6337,7 @@
         <v>75</v>
       </c>
       <c r="E48">
-        <v>0.12958704000000001</v>
+        <v>0.13087008</v>
       </c>
       <c r="F48">
         <v>3144</v>
@@ -6393,7 +6393,7 @@
         <v>75</v>
       </c>
       <c r="E49">
-        <v>0.12958704000000001</v>
+        <v>0.13087008</v>
       </c>
       <c r="F49">
         <v>3144</v>
@@ -6449,7 +6449,7 @@
         <v>75</v>
       </c>
       <c r="E50">
-        <v>0.12958704000000001</v>
+        <v>0.13087008</v>
       </c>
       <c r="F50">
         <v>3144</v>
@@ -6505,7 +6505,7 @@
         <v>75</v>
       </c>
       <c r="E51">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F51">
         <v>3144</v>
@@ -6561,7 +6561,7 @@
         <v>75</v>
       </c>
       <c r="E52">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F52">
         <v>3144</v>
@@ -6617,7 +6617,7 @@
         <v>82</v>
       </c>
       <c r="E53">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F53">
         <v>3144</v>
@@ -6673,7 +6673,7 @@
         <v>82</v>
       </c>
       <c r="E54">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F54">
         <v>3144</v>
@@ -6729,7 +6729,7 @@
         <v>82</v>
       </c>
       <c r="E55">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F55">
         <v>3144</v>
@@ -6785,7 +6785,7 @@
         <v>82</v>
       </c>
       <c r="E56">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F56">
         <v>3144</v>
@@ -6841,7 +6841,7 @@
         <v>87</v>
       </c>
       <c r="E57">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F57">
         <v>3144</v>
@@ -6897,7 +6897,7 @@
         <v>87</v>
       </c>
       <c r="E58">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F58">
         <v>3144</v>
@@ -6953,7 +6953,7 @@
         <v>90</v>
       </c>
       <c r="E59">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F59">
         <v>3144</v>
@@ -7009,7 +7009,7 @@
         <v>92</v>
       </c>
       <c r="E60">
-        <v>9.1375103999999999E-2</v>
+        <v>9.2279808000000005E-2</v>
       </c>
       <c r="F60">
         <v>3583</v>
@@ -7065,7 +7065,7 @@
         <v>92</v>
       </c>
       <c r="E61">
-        <v>0.12566015999999999</v>
+        <v>0.12690431999999999</v>
       </c>
       <c r="F61">
         <v>3144</v>
@@ -7121,7 +7121,7 @@
         <v>92</v>
       </c>
       <c r="E62">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F62">
         <v>3144</v>
@@ -7177,7 +7177,7 @@
         <v>92</v>
       </c>
       <c r="E63">
-        <v>0.17243366399999999</v>
+        <v>0.174140928</v>
       </c>
       <c r="F63">
         <v>2757</v>
@@ -7233,7 +7233,7 @@
         <v>97</v>
       </c>
       <c r="E64">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F64">
         <v>1967</v>
@@ -7289,7 +7289,7 @@
         <v>97</v>
       </c>
       <c r="E65">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F65">
         <v>1967</v>
@@ -7345,7 +7345,7 @@
         <v>100</v>
       </c>
       <c r="E66">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F66">
         <v>1967</v>
@@ -7401,7 +7401,7 @@
         <v>100</v>
       </c>
       <c r="E67">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F67">
         <v>1967</v>
@@ -7457,7 +7457,7 @@
         <v>71</v>
       </c>
       <c r="E68">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F68">
         <v>3144</v>
@@ -7513,7 +7513,7 @@
         <v>71</v>
       </c>
       <c r="E69">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F69">
         <v>3144</v>
@@ -7569,7 +7569,7 @@
         <v>105</v>
       </c>
       <c r="E70">
-        <v>0.12958704000000001</v>
+        <v>0.13087008</v>
       </c>
       <c r="F70">
         <v>3144</v>
@@ -7625,7 +7625,7 @@
         <v>105</v>
       </c>
       <c r="E71">
-        <v>0.13351392000000001</v>
+        <v>0.13483584000000001</v>
       </c>
       <c r="F71">
         <v>3144</v>
@@ -7681,7 +7681,7 @@
         <v>45</v>
       </c>
       <c r="E72">
-        <v>0.26632972799999999</v>
+        <v>0.26896665599999997</v>
       </c>
       <c r="F72">
         <v>1967</v>
@@ -7737,7 +7737,7 @@
         <v>45</v>
       </c>
       <c r="E73">
-        <v>0.30701899199999999</v>
+        <v>0.31005878399999998</v>
       </c>
       <c r="F73">
         <v>1967</v>
@@ -7793,7 +7793,7 @@
         <v>45</v>
       </c>
       <c r="E74">
-        <v>0.30701899199999994</v>
+        <v>0.31005878399999998</v>
       </c>
       <c r="F74">
         <v>1967</v>
@@ -7849,7 +7849,7 @@
         <v>45</v>
       </c>
       <c r="E75">
-        <v>0.30701899199999994</v>
+        <v>0.31005878399999998</v>
       </c>
       <c r="F75">
         <v>1967</v>
@@ -7905,7 +7905,7 @@
         <v>112</v>
       </c>
       <c r="E76">
-        <v>0.31441703999999998</v>
+        <v>0.31753007999999999</v>
       </c>
       <c r="F76">
         <v>1967</v>
@@ -7961,7 +7961,7 @@
         <v>112</v>
       </c>
       <c r="E77">
-        <v>0.31441703999999998</v>
+        <v>0.31753007999999999</v>
       </c>
       <c r="F77">
         <v>1967</v>
@@ -8017,7 +8017,7 @@
         <v>68</v>
       </c>
       <c r="E78">
-        <v>0.31441703999999998</v>
+        <v>0.31753007999999999</v>
       </c>
       <c r="F78">
         <v>1967</v>
@@ -8073,7 +8073,7 @@
         <v>68</v>
       </c>
       <c r="E79">
-        <v>0.31441703999999998</v>
+        <v>0.31753007999999999</v>
       </c>
       <c r="F79">
         <v>1967</v>
@@ -8129,7 +8129,7 @@
         <v>117</v>
       </c>
       <c r="E80">
-        <v>0.34820760000000001</v>
+        <v>0.3516552</v>
       </c>
       <c r="F80">
         <v>1726</v>
@@ -8185,7 +8185,7 @@
         <v>117</v>
       </c>
       <c r="E81">
-        <v>0.34820760000000006</v>
+        <v>0.3516552</v>
       </c>
       <c r="F81">
         <v>1726</v>
@@ -8241,7 +8241,7 @@
         <v>105</v>
       </c>
       <c r="E82">
-        <v>0.31441703999999998</v>
+        <v>0.31753007999999999</v>
       </c>
       <c r="F82">
         <v>1967</v>
@@ -8297,7 +8297,7 @@
         <v>105</v>
       </c>
       <c r="E83">
-        <v>0.31441703999999998</v>
+        <v>0.31753007999999999</v>
       </c>
       <c r="F83">
         <v>1967</v>
@@ -8353,7 +8353,7 @@
         <v>87</v>
       </c>
       <c r="E84">
-        <v>0.31441703999999998</v>
+        <v>0.31753007999999999</v>
       </c>
       <c r="F84">
         <v>1967</v>
@@ -8409,7 +8409,7 @@
         <v>87</v>
       </c>
       <c r="E85">
-        <v>0.31441703999999998</v>
+        <v>0.31753007999999999</v>
       </c>
       <c r="F85">
         <v>1967</v>
@@ -8465,7 +8465,7 @@
         <v>124</v>
       </c>
       <c r="E86">
-        <v>0.34820760000000001</v>
+        <v>0.3516552</v>
       </c>
       <c r="F86">
         <v>1726</v>
@@ -8521,7 +8521,7 @@
         <v>124</v>
       </c>
       <c r="E87">
-        <v>0.34820760000000001</v>
+        <v>0.3516552</v>
       </c>
       <c r="F87">
         <v>1726</v>
@@ -8577,7 +8577,7 @@
         <v>97</v>
       </c>
       <c r="E88">
-        <v>0.30701899199999994</v>
+        <v>0.31005878399999998</v>
       </c>
       <c r="F88">
         <v>1967</v>
@@ -8633,7 +8633,7 @@
         <v>97</v>
       </c>
       <c r="E89">
-        <v>0.30701899199999994</v>
+        <v>0.31005878399999998</v>
       </c>
       <c r="F89">
         <v>1967</v>
@@ -8689,7 +8689,7 @@
         <v>97</v>
       </c>
       <c r="E90">
-        <v>0.30701899199999994</v>
+        <v>0.31005878399999998</v>
       </c>
       <c r="F90">
         <v>1967</v>
@@ -8745,7 +8745,7 @@
         <v>97</v>
       </c>
       <c r="E91">
-        <v>0.30701899199999994</v>
+        <v>0.31005878399999998</v>
       </c>
       <c r="F91">
         <v>1967</v>
@@ -8801,7 +8801,7 @@
         <v>97</v>
       </c>
       <c r="E92">
-        <v>0.32181508799999997</v>
+        <v>0.32500137599999995</v>
       </c>
       <c r="F92">
         <v>1967</v>
@@ -8857,7 +8857,7 @@
         <v>100</v>
       </c>
       <c r="E93">
-        <v>0.32921313599999996</v>
+        <v>0.33247267199999997</v>
       </c>
       <c r="F93">
         <v>1967</v>
@@ -8913,7 +8913,7 @@
         <v>100</v>
       </c>
       <c r="E94">
-        <v>0.32921313599999996</v>
+        <v>0.33247267199999997</v>
       </c>
       <c r="F94">
         <v>1967</v>
@@ -10252,7 +10252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1240CBE4-2474-48D1-B962-438CA0682886}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F77E960-3494-465A-8737-ADC875714794}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18538,7 +18538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69917601-E1E8-4099-B6B6-09643A783910}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B8A1C3-9971-45DB-8CC9-82ACFD452EC3}">
   <dimension ref="B9:T399"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18623,7 +18623,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="G11">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H11">
         <v>2817.4999999999995</v>
@@ -18676,7 +18676,7 @@
         <v>0.03</v>
       </c>
       <c r="G12">
-        <v>0.31027199999999999</v>
+        <v>0.31334399999999996</v>
       </c>
       <c r="H12">
         <v>3307.5</v>
@@ -18726,10 +18726,10 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>6.9512195121951212E-2</v>
+        <v>7.184176829268292E-2</v>
       </c>
       <c r="G13">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H13">
         <v>2817.4999999999995</v>
@@ -18782,7 +18782,7 @@
         <v>0.03</v>
       </c>
       <c r="G14">
-        <v>0.31027199999999999</v>
+        <v>0.31334399999999996</v>
       </c>
       <c r="H14">
         <v>3307.5</v>
@@ -18832,10 +18832,10 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.22475609756097559</v>
+        <v>0.23228838414634145</v>
       </c>
       <c r="G15">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H15">
         <v>2817.4999999999995</v>
@@ -18888,7 +18888,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G16">
-        <v>0.31027199999999999</v>
+        <v>0.31334399999999996</v>
       </c>
       <c r="H16">
         <v>3307.5</v>
@@ -18938,19 +18938,19 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>8.5731707317073177E-2</v>
+        <v>8.8604847560975614E-2</v>
       </c>
       <c r="G17">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H17">
         <v>2817.4999999999995</v>
       </c>
       <c r="I17">
-        <v>107.25000000000001</v>
+        <v>107.25</v>
       </c>
       <c r="J17">
-        <v>7.0400000000000009</v>
+        <v>7.0400000000000018</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -18994,7 +18994,7 @@
         <v>0.05</v>
       </c>
       <c r="G18">
-        <v>0.33451199999999992</v>
+        <v>0.33782399999999996</v>
       </c>
       <c r="H18">
         <v>2173.5</v>
@@ -19047,7 +19047,7 @@
         <v>0.05</v>
       </c>
       <c r="G19">
-        <v>0.33451199999999992</v>
+        <v>0.33782399999999996</v>
       </c>
       <c r="H19">
         <v>2173.5</v>
@@ -19100,7 +19100,7 @@
         <v>0.34</v>
       </c>
       <c r="G20">
-        <v>0.36359999999999998</v>
+        <v>0.36719999999999997</v>
       </c>
       <c r="H20">
         <v>1610</v>
@@ -19153,7 +19153,7 @@
         <v>0.34</v>
       </c>
       <c r="G21">
-        <v>0.36359999999999998</v>
+        <v>0.36719999999999997</v>
       </c>
       <c r="H21">
         <v>1610</v>
@@ -19206,7 +19206,7 @@
         <v>0.22</v>
       </c>
       <c r="G22">
-        <v>0.34420800000000001</v>
+        <v>0.34761599999999993</v>
       </c>
       <c r="H22">
         <v>1851.4999999999998</v>
@@ -19259,7 +19259,7 @@
         <v>0.22</v>
       </c>
       <c r="G23">
-        <v>0.34420800000000001</v>
+        <v>0.34761599999999993</v>
       </c>
       <c r="H23">
         <v>1851.4999999999998</v>
@@ -19312,7 +19312,7 @@
         <v>0.11</v>
       </c>
       <c r="G24">
-        <v>0.353904</v>
+        <v>0.357408</v>
       </c>
       <c r="H24">
         <v>1851.4999999999998</v>
@@ -19365,7 +19365,7 @@
         <v>0.11</v>
       </c>
       <c r="G25">
-        <v>0.33451199999999998</v>
+        <v>0.33782399999999996</v>
       </c>
       <c r="H25">
         <v>1851.4999999999998</v>
@@ -19418,7 +19418,7 @@
         <v>0.11</v>
       </c>
       <c r="G26">
-        <v>0.33451199999999998</v>
+        <v>0.33782399999999996</v>
       </c>
       <c r="H26">
         <v>1851.4999999999998</v>
@@ -19471,7 +19471,7 @@
         <v>0.3</v>
       </c>
       <c r="G27">
-        <v>0.34420800000000001</v>
+        <v>0.34761599999999998</v>
       </c>
       <c r="H27">
         <v>1851.4999999999995</v>
@@ -19524,7 +19524,7 @@
         <v>0.3</v>
       </c>
       <c r="G28">
-        <v>0.34420800000000001</v>
+        <v>0.34761599999999998</v>
       </c>
       <c r="H28">
         <v>1851.4999999999995</v>
@@ -19577,7 +19577,7 @@
         <v>3.0000000000001137E-3</v>
       </c>
       <c r="G29">
-        <v>0.33454230000000007</v>
+        <v>0.3378546</v>
       </c>
       <c r="K29">
         <v>33</v>
@@ -19621,7 +19621,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
       <c r="G30">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H30">
         <v>1610</v>
@@ -19674,7 +19674,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
       <c r="G31">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H31">
         <v>1610</v>
@@ -19727,7 +19727,7 @@
         <v>0.62250000000000005</v>
       </c>
       <c r="G32">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H32">
         <v>1400</v>
@@ -19780,7 +19780,7 @@
         <v>0.62250000000000005</v>
       </c>
       <c r="G33">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H33">
         <v>1400</v>
@@ -19833,7 +19833,7 @@
         <v>0.6</v>
       </c>
       <c r="G34">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H34">
         <v>1400</v>
@@ -19886,7 +19886,7 @@
         <v>0.15</v>
       </c>
       <c r="G35">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H35">
         <v>1610</v>
@@ -19939,7 +19939,7 @@
         <v>0.15</v>
       </c>
       <c r="G36">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H36">
         <v>1610</v>
@@ -19992,7 +19992,7 @@
         <v>0.15</v>
       </c>
       <c r="G37">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H37">
         <v>1610</v>
@@ -20045,7 +20045,7 @@
         <v>0.6</v>
       </c>
       <c r="G38">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H38">
         <v>1400</v>
@@ -20098,7 +20098,7 @@
         <v>0.6</v>
       </c>
       <c r="G39">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H39">
         <v>1400</v>
@@ -20151,7 +20151,7 @@
         <v>0.3</v>
       </c>
       <c r="G40">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H40">
         <v>1610</v>
@@ -20204,7 +20204,7 @@
         <v>0.3</v>
       </c>
       <c r="G41">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H41">
         <v>1610</v>
@@ -20257,7 +20257,7 @@
         <v>0.3</v>
       </c>
       <c r="G42">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H42">
         <v>1610</v>
@@ -20310,7 +20310,7 @@
         <v>0.3</v>
       </c>
       <c r="G43">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H43">
         <v>1610</v>
@@ -20363,7 +20363,7 @@
         <v>0.54</v>
       </c>
       <c r="G44">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H44">
         <v>1400</v>
@@ -20416,7 +20416,7 @@
         <v>0.54</v>
       </c>
       <c r="G45">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H45">
         <v>1400</v>
@@ -20469,7 +20469,7 @@
         <v>0.62</v>
       </c>
       <c r="G46">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H46">
         <v>1400</v>
@@ -20522,7 +20522,7 @@
         <v>0.62</v>
       </c>
       <c r="G47">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H47">
         <v>1400</v>
@@ -20575,7 +20575,7 @@
         <v>0.05</v>
       </c>
       <c r="G48">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H48">
         <v>1889.9999999999998</v>
@@ -20628,7 +20628,7 @@
         <v>0.05</v>
       </c>
       <c r="G49">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H49">
         <v>1889.9999999999998</v>
@@ -20681,7 +20681,7 @@
         <v>0.3</v>
       </c>
       <c r="G50">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H50">
         <v>1610</v>
@@ -20734,7 +20734,7 @@
         <v>0.3</v>
       </c>
       <c r="G51">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H51">
         <v>1610</v>
@@ -20787,7 +20787,7 @@
         <v>0.15</v>
       </c>
       <c r="G52">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H52">
         <v>1610</v>
@@ -20840,7 +20840,7 @@
         <v>0.03</v>
       </c>
       <c r="G53">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H53">
         <v>1889.9999999999998</v>
@@ -20893,7 +20893,7 @@
         <v>0.11</v>
       </c>
       <c r="G54">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H54">
         <v>1610</v>
@@ -20946,7 +20946,7 @@
         <v>0.11</v>
       </c>
       <c r="G55">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H55">
         <v>1610</v>
@@ -20999,7 +20999,7 @@
         <v>0.11</v>
       </c>
       <c r="G56">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H56">
         <v>1610</v>
@@ -21052,7 +21052,7 @@
         <v>0.11</v>
       </c>
       <c r="G57">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H57">
         <v>1610</v>
@@ -21105,7 +21105,7 @@
         <v>0.3</v>
       </c>
       <c r="G58">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H58">
         <v>1610</v>
@@ -21158,7 +21158,7 @@
         <v>0.3</v>
       </c>
       <c r="G59">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H59">
         <v>1610</v>
@@ -21211,7 +21211,7 @@
         <v>0.3</v>
       </c>
       <c r="G60">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H60">
         <v>1610</v>
@@ -21264,7 +21264,7 @@
         <v>0.3</v>
       </c>
       <c r="G61">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H61">
         <v>1610</v>
@@ -21317,7 +21317,7 @@
         <v>0.3</v>
       </c>
       <c r="G62">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H62">
         <v>1610</v>
@@ -21370,7 +21370,7 @@
         <v>0.3</v>
       </c>
       <c r="G63">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H63">
         <v>1610</v>
@@ -21423,7 +21423,7 @@
         <v>0.3</v>
       </c>
       <c r="G64">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H64">
         <v>1610</v>
@@ -21476,7 +21476,7 @@
         <v>0.3</v>
       </c>
       <c r="G65">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H65">
         <v>1610</v>
@@ -21529,7 +21529,7 @@
         <v>0.06</v>
       </c>
       <c r="G66">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H66">
         <v>1610</v>
@@ -21582,7 +21582,7 @@
         <v>0.05</v>
       </c>
       <c r="G67">
-        <v>0.30057599999999995</v>
+        <v>0.30355199999999999</v>
       </c>
       <c r="H67">
         <v>1889.9999999999998</v>
@@ -21635,7 +21635,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G68">
-        <v>0.31027199999999999</v>
+        <v>0.31334399999999996</v>
       </c>
       <c r="H68">
         <v>1610</v>
@@ -21688,7 +21688,7 @@
         <v>0.3</v>
       </c>
       <c r="G69">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H69">
         <v>1610</v>
@@ -21741,7 +21741,7 @@
         <v>0.33</v>
       </c>
       <c r="G70">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H70">
         <v>1400</v>
@@ -21794,7 +21794,7 @@
         <v>0.6</v>
       </c>
       <c r="G71">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H71">
         <v>1400</v>
@@ -21847,7 +21847,7 @@
         <v>0.6</v>
       </c>
       <c r="G72">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H72">
         <v>1400</v>
@@ -21900,7 +21900,7 @@
         <v>0.6</v>
       </c>
       <c r="G73">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H73">
         <v>1400</v>
@@ -21953,7 +21953,7 @@
         <v>0.6</v>
       </c>
       <c r="G74">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H74">
         <v>1400</v>
@@ -22006,7 +22006,7 @@
         <v>0.15</v>
       </c>
       <c r="G75">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H75">
         <v>1610</v>
@@ -22059,7 +22059,7 @@
         <v>0.15</v>
       </c>
       <c r="G76">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H76">
         <v>1610</v>
@@ -22112,7 +22112,7 @@
         <v>0.05</v>
       </c>
       <c r="G77">
-        <v>0.31996800000000003</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H77">
         <v>1889.9999999999998</v>
@@ -22165,7 +22165,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G78">
-        <v>0.32966400000000001</v>
+        <v>0.33292800000000006</v>
       </c>
       <c r="H78">
         <v>1610</v>
@@ -22218,7 +22218,7 @@
         <v>0.6</v>
       </c>
       <c r="G79">
-        <v>0.34905599999999998</v>
+        <v>0.35251199999999999</v>
       </c>
       <c r="H79">
         <v>1400</v>
@@ -22271,7 +22271,7 @@
         <v>0.68799999999999994</v>
       </c>
       <c r="G80">
-        <v>0.40238400000000002</v>
+        <v>0.40636800000000001</v>
       </c>
       <c r="H80">
         <v>1540</v>
@@ -22324,7 +22324,7 @@
         <v>0.62250000000000005</v>
       </c>
       <c r="G81">
-        <v>0.40238399999999996</v>
+        <v>0.40636800000000001</v>
       </c>
       <c r="H81">
         <v>1540</v>
@@ -22377,7 +22377,7 @@
         <v>0.62250000000000005</v>
       </c>
       <c r="G82">
-        <v>0.40238399999999996</v>
+        <v>0.40636800000000001</v>
       </c>
       <c r="H82">
         <v>1540</v>
@@ -22430,7 +22430,7 @@
         <v>0.6</v>
       </c>
       <c r="G83">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H83">
         <v>1540</v>
@@ -22483,7 +22483,7 @@
         <v>0.6</v>
       </c>
       <c r="G84">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H84">
         <v>1540</v>
@@ -22536,7 +22536,7 @@
         <v>0.66</v>
       </c>
       <c r="G85">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H85">
         <v>1540</v>
@@ -22589,7 +22589,7 @@
         <v>0.66</v>
       </c>
       <c r="G86">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H86">
         <v>1540</v>
@@ -22642,7 +22642,7 @@
         <v>0.70099999999999996</v>
       </c>
       <c r="G87">
-        <v>0.41208</v>
+        <v>0.41616000000000003</v>
       </c>
       <c r="H87">
         <v>1540</v>
@@ -22695,7 +22695,7 @@
         <v>0.70199999999999996</v>
       </c>
       <c r="G88">
-        <v>0.41208000000000006</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H88">
         <v>1540</v>
@@ -22748,7 +22748,7 @@
         <v>0.6</v>
       </c>
       <c r="G89">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H89">
         <v>1540</v>
@@ -22801,7 +22801,7 @@
         <v>0.6</v>
       </c>
       <c r="G90">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H90">
         <v>1540</v>
@@ -22854,7 +22854,7 @@
         <v>0.6</v>
       </c>
       <c r="G91">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H91">
         <v>1540</v>
@@ -22907,7 +22907,7 @@
         <v>0.6</v>
       </c>
       <c r="G92">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H92">
         <v>1540</v>
@@ -22960,7 +22960,7 @@
         <v>0.71599999999999997</v>
       </c>
       <c r="G93">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H93">
         <v>1540</v>
@@ -23013,7 +23013,7 @@
         <v>0.71599999999999997</v>
       </c>
       <c r="G94">
-        <v>0.41208</v>
+        <v>0.41615999999999997</v>
       </c>
       <c r="H94">
         <v>1540</v>
@@ -23066,7 +23066,7 @@
         <v>0.622</v>
       </c>
       <c r="G95">
-        <v>0.40238399999999996</v>
+        <v>0.40636800000000001</v>
       </c>
       <c r="H95">
         <v>1540</v>
@@ -23119,7 +23119,7 @@
         <v>0.622</v>
       </c>
       <c r="G96">
-        <v>0.40238399999999996</v>
+        <v>0.40636800000000001</v>
       </c>
       <c r="H96">
         <v>1540</v>
@@ -23172,7 +23172,7 @@
         <v>0.6</v>
       </c>
       <c r="G97">
-        <v>0.40238399999999996</v>
+        <v>0.40636800000000001</v>
       </c>
       <c r="H97">
         <v>1540</v>
@@ -23225,7 +23225,7 @@
         <v>0.6</v>
       </c>
       <c r="G98">
-        <v>0.40238399999999996</v>
+        <v>0.40636800000000001</v>
       </c>
       <c r="H98">
         <v>1540</v>
@@ -23278,7 +23278,7 @@
         <v>0.6</v>
       </c>
       <c r="G99">
-        <v>0.42177599999999998</v>
+        <v>0.425952</v>
       </c>
       <c r="H99">
         <v>1680</v>
@@ -23331,7 +23331,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G100">
-        <v>0.43147199999999997</v>
+        <v>0.43574399999999996</v>
       </c>
       <c r="H100">
         <v>1680</v>
@@ -23384,7 +23384,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G101">
-        <v>0.43147199999999997</v>
+        <v>0.43574399999999996</v>
       </c>
       <c r="H101">
         <v>1680</v>
@@ -32504,7 +32504,7 @@
         <v>400</v>
       </c>
       <c r="P284" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q284" t="s">
         <v>471</v>
@@ -32560,7 +32560,7 @@
         <v>400</v>
       </c>
       <c r="P285" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q285" t="s">
         <v>471</v>
@@ -33904,7 +33904,7 @@
         <v>432</v>
       </c>
       <c r="P309" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q309" t="s">
         <v>471</v>
@@ -33960,7 +33960,7 @@
         <v>432</v>
       </c>
       <c r="P310" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q310" t="s">
         <v>471</v>
@@ -34072,7 +34072,7 @@
         <v>437</v>
       </c>
       <c r="P312" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q312" t="s">
         <v>471</v>
@@ -34128,7 +34128,7 @@
         <v>437</v>
       </c>
       <c r="P313" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q313" t="s">
         <v>471</v>
@@ -34184,7 +34184,7 @@
         <v>439</v>
       </c>
       <c r="P314" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q314" t="s">
         <v>471</v>
@@ -34240,7 +34240,7 @@
         <v>439</v>
       </c>
       <c r="P315" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q315" t="s">
         <v>471</v>
@@ -34296,7 +34296,7 @@
         <v>441</v>
       </c>
       <c r="P316" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q316" t="s">
         <v>471</v>
@@ -34352,7 +34352,7 @@
         <v>441</v>
       </c>
       <c r="P317" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q317" t="s">
         <v>471</v>
@@ -37537,7 +37537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F4BEA1-C3CD-4519-9F32-13A1FBF24DFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD93956-B27B-4053-AD43-3EC6DEE1120A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_VNM_grids_kan/vt_vervestacks_VNM_v1.xlsx
+++ b/VerveStacks_VNM_grids_kan/vt_vervestacks_VNM_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C72A6E0C-8663-4D1B-B50A-75D5A5DF113A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FC8A297-03C2-48A0-807D-153F4A37F599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{930809CF-90FC-411C-81D2-FB561E31C520}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{901974E5-34F7-4B28-A0FD-3508F6982914}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4186,7 +4186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DD836A-BF91-4DF7-BEC5-3FD283E16575}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F52BF0E-6D3D-4F1F-B80F-0DBED07DDA07}">
   <dimension ref="B9:T117"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10252,7 +10252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F77E960-3494-465A-8737-ADC875714794}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A37BC1D-7E90-495F-8662-EB8C7344ABA2}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18538,7 +18538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B8A1C3-9971-45DB-8CC9-82ACFD452EC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE59EA2F-3475-4C60-B564-E347689EEF5B}">
   <dimension ref="B9:T399"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31953,7 +31953,7 @@
         <v>33</v>
       </c>
       <c r="L274">
-        <v>0.18682856720731586</v>
+        <v>0.18682856720731583</v>
       </c>
       <c r="N274" t="s">
         <v>469</v>
@@ -32000,7 +32000,7 @@
         <v>33</v>
       </c>
       <c r="L275">
-        <v>0.18682856720731586</v>
+        <v>0.18682856720731583</v>
       </c>
       <c r="N275" t="s">
         <v>469</v>
@@ -32047,7 +32047,7 @@
         <v>33</v>
       </c>
       <c r="L276">
-        <v>0.18682856720731586</v>
+        <v>0.18682856720731583</v>
       </c>
       <c r="N276" t="s">
         <v>469</v>
@@ -33904,7 +33904,7 @@
         <v>432</v>
       </c>
       <c r="P309" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q309" t="s">
         <v>471</v>
@@ -33960,7 +33960,7 @@
         <v>432</v>
       </c>
       <c r="P310" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q310" t="s">
         <v>471</v>
@@ -34184,7 +34184,7 @@
         <v>439</v>
       </c>
       <c r="P314" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q314" t="s">
         <v>471</v>
@@ -34240,7 +34240,7 @@
         <v>439</v>
       </c>
       <c r="P315" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q315" t="s">
         <v>471</v>
@@ -34296,7 +34296,7 @@
         <v>441</v>
       </c>
       <c r="P316" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q316" t="s">
         <v>471</v>
@@ -34352,7 +34352,7 @@
         <v>441</v>
       </c>
       <c r="P317" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q317" t="s">
         <v>471</v>
@@ -34576,7 +34576,7 @@
         <v>450</v>
       </c>
       <c r="P321" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q321" t="s">
         <v>471</v>
@@ -34632,7 +34632,7 @@
         <v>450</v>
       </c>
       <c r="P322" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q322" t="s">
         <v>471</v>
@@ -37537,7 +37537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD93956-B27B-4053-AD43-3EC6DEE1120A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2222729-E713-47E4-9BF7-7A0CD7E1E814}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_VNM_grids_kan/vt_vervestacks_VNM_v1.xlsx
+++ b/VerveStacks_VNM_grids_kan/vt_vervestacks_VNM_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FC8A297-03C2-48A0-807D-153F4A37F599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1A45266-B72C-4A2A-8B11-1A7BB353558C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{901974E5-34F7-4B28-A0FD-3508F6982914}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D7390DCA-1169-467F-92E8-71CCB9B0C9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4186,7 +4186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F52BF0E-6D3D-4F1F-B80F-0DBED07DDA07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A119C7-C172-4EA7-B837-F86A7F7B5F6E}">
   <dimension ref="B9:T117"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10252,7 +10252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A37BC1D-7E90-495F-8662-EB8C7344ABA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EAC6224-1B02-4BAA-9098-AB11C9A586C2}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18538,7 +18538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE59EA2F-3475-4C60-B564-E347689EEF5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{633C0777-2FAD-44F5-9FCE-8D7E2B3383B4}">
   <dimension ref="B9:T399"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31953,7 +31953,7 @@
         <v>33</v>
       </c>
       <c r="L274">
-        <v>0.18682856720731583</v>
+        <v>0.18682856720731586</v>
       </c>
       <c r="N274" t="s">
         <v>469</v>
@@ -32000,7 +32000,7 @@
         <v>33</v>
       </c>
       <c r="L275">
-        <v>0.18682856720731583</v>
+        <v>0.18682856720731586</v>
       </c>
       <c r="N275" t="s">
         <v>469</v>
@@ -32047,7 +32047,7 @@
         <v>33</v>
       </c>
       <c r="L276">
-        <v>0.18682856720731583</v>
+        <v>0.18682856720731586</v>
       </c>
       <c r="N276" t="s">
         <v>469</v>
@@ -33904,7 +33904,7 @@
         <v>432</v>
       </c>
       <c r="P309" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q309" t="s">
         <v>471</v>
@@ -33960,7 +33960,7 @@
         <v>432</v>
       </c>
       <c r="P310" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q310" t="s">
         <v>471</v>
@@ -34184,7 +34184,7 @@
         <v>439</v>
       </c>
       <c r="P314" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q314" t="s">
         <v>471</v>
@@ -34240,7 +34240,7 @@
         <v>439</v>
       </c>
       <c r="P315" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q315" t="s">
         <v>471</v>
@@ -34576,7 +34576,7 @@
         <v>450</v>
       </c>
       <c r="P321" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q321" t="s">
         <v>471</v>
@@ -34632,7 +34632,7 @@
         <v>450</v>
       </c>
       <c r="P322" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q322" t="s">
         <v>471</v>
@@ -37537,7 +37537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2222729-E713-47E4-9BF7-7A0CD7E1E814}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022D2F71-42B5-4470-B0CF-60EB2B0448D3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_VNM_grids_kan/vt_vervestacks_VNM_v1.xlsx
+++ b/VerveStacks_VNM_grids_kan/vt_vervestacks_VNM_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1A45266-B72C-4A2A-8B11-1A7BB353558C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8A047F3-9EA8-48D0-B898-F2E219F1C846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D7390DCA-1169-467F-92E8-71CCB9B0C9DC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8CE2E6C6-B679-49FF-B04D-1CCF24A7C614}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4186,7 +4186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A119C7-C172-4EA7-B837-F86A7F7B5F6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE366B3-746D-4440-8737-3CAC35CCB58D}">
   <dimension ref="B9:T117"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10252,7 +10252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EAC6224-1B02-4BAA-9098-AB11C9A586C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9CFA248-8BEA-47A1-BEC7-4A9870742969}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18538,7 +18538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{633C0777-2FAD-44F5-9FCE-8D7E2B3383B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A87FD4-5F91-4720-A2E9-16AC3D5B2E8F}">
   <dimension ref="B9:T399"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34184,7 +34184,7 @@
         <v>439</v>
       </c>
       <c r="P314" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q314" t="s">
         <v>471</v>
@@ -34240,7 +34240,7 @@
         <v>439</v>
       </c>
       <c r="P315" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q315" t="s">
         <v>471</v>
@@ -34296,7 +34296,7 @@
         <v>441</v>
       </c>
       <c r="P316" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q316" t="s">
         <v>471</v>
@@ -34352,7 +34352,7 @@
         <v>441</v>
       </c>
       <c r="P317" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q317" t="s">
         <v>471</v>
@@ -34576,7 +34576,7 @@
         <v>450</v>
       </c>
       <c r="P321" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="Q321" t="s">
         <v>471</v>
@@ -34632,7 +34632,7 @@
         <v>450</v>
       </c>
       <c r="P322" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="Q322" t="s">
         <v>471</v>
@@ -37537,7 +37537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022D2F71-42B5-4470-B0CF-60EB2B0448D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDB3A4F1-F409-4B1F-856A-4DFE141CA101}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
